--- a/data/trans_orig/IP11D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116781</t>
+          <t>116675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153992</t>
+          <t>153881</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158713</t>
+          <t>158710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179587</t>
+          <t>179421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335731</t>
+          <t>335338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340919</t>
+          <t>340859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166059</t>
+          <t>165843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172014</t>
+          <t>171982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202779</t>
+          <t>203019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210819</t>
+          <t>210805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373274</t>
+          <t>372779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381873</t>
+          <t>381738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>271712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>292487</t>
+          <t>291095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303642</t>
+          <t>303432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>567434</t>
+          <t>567002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579057</t>
+          <t>578425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,47 +2152,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>9123</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>24445</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>15080</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>9056</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>24495</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>654846</t>
+          <t>654836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>662819</t>
+          <t>662467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742766</t>
+          <t>743236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756143</t>
+          <t>756256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1401508</t>
+          <t>1401558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1416947</t>
+          <t>1416880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP11D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>57086</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55324</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>51642</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49637</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,29%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>224</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>118530</t>
+          <t>102179</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116675</t>
+          <t>100351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5418</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>156865</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>155268</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>157402</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>153881</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158710</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>181673</t>
+          <t>143680</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179421</t>
+          <t>140358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>144955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>339075</t>
+          <t>300544</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335338</t>
+          <t>296956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340859</t>
+          <t>302241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2899</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7256</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6845</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>196268</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>191911</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>198490</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>170351</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>165843</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171982</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>208295</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>203019</t>
+          <t>167887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210805</t>
+          <t>173627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378647</t>
+          <t>368189</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372779</t>
+          <t>362823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381738</t>
+          <t>371169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199167</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199167</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199167</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>172688</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>172688</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>172688</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211565</t>
+          <t>174323</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211565</t>
+          <t>174323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211565</t>
+          <t>174323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384253</t>
+          <t>373490</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384253</t>
+          <t>373490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384253</t>
+          <t>373490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5079</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11168</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3746</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4076</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2051</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14388</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>287566</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>281477</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>291062</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>274723</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>271712</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>255787</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>252477</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>256553</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>299947</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>291095</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>303432</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,29%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>678</t>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>574669</t>
+          <t>543353</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>567002</t>
+          <t>535965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578425</t>
+          <t>546715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8635</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16081</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10120</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24445</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>691235</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683789</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>695476</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>659562</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>654836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>662467</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>751360</t>
+          <t>623030</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743236</t>
+          <t>617765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756256</t>
+          <t>626065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1410923</t>
+          <t>1314265</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1401558</t>
+          <t>1305083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1416880</t>
+          <t>1319314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664956</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>628484</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426003</t>
+          <t>1328354</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
